--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 18/08/2026, 15:38</x:t>
+    <x:t>Conta: 18466421 | 24/08/2026, 09:28</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 24/08/2026, 09:28</x:t>
+    <x:t>Conta: 18466421 | 25/08/2026, 19:18</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 25/08/2026, 19:18</x:t>
+    <x:t>Conta: 18466421 | 28/08/2026, 09:30</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 28/08/2026, 09:30</x:t>
+    <x:t>Conta: 18466421 | 31/08/2026, 17:20</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 31/08/2026, 17:20</x:t>
+    <x:t>Conta: 18466421 | 01/09/2026, 16:01</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 01/09/2026, 16:01</x:t>
+    <x:t>Conta: 18466421 | 04/09/2026, 14:13</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
